--- a/reports/seo_intel_2026-W21.xlsx
+++ b/reports/seo_intel_2026-W21.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:15 UTC</t>
+          <t>Generated: 2026-05-18 12:40 UTC</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:15 UTC</t>
+          <t>Generated: 2026-05-18 12:40 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/seo_intel_2026-W21.xlsx
+++ b/reports/seo_intel_2026-W21.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:40 UTC</t>
+          <t>Generated: 2026-05-18 14:00 UTC</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 12:40 UTC</t>
+          <t>Generated: 2026-05-18 14:00 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/seo_intel_2026-W21.xlsx
+++ b/reports/seo_intel_2026-W21.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 14:00 UTC</t>
+          <t>Generated: 2026-05-18 18:37 UTC</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 14:00 UTC</t>
+          <t>Generated: 2026-05-18 18:37 UTC</t>
         </is>
       </c>
     </row>

--- a/reports/seo_intel_2026-W21.xlsx
+++ b/reports/seo_intel_2026-W21.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 18:37 UTC</t>
+          <t>Generated: 2026-05-19 17:39 UTC</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-18 18:37 UTC</t>
+          <t>Generated: 2026-05-19 17:39 UTC</t>
         </is>
       </c>
     </row>
